--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1844.33</v>
+        <v>1828.71</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1411.83</v>
+        <v>1399.87</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>782.27</v>
+        <v>775.65</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1474.67</v>
+        <v>1462.18</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1526.26</v>
+        <v>1513.34</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4131.16</v>
+        <v>4096.17</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1346.81</v>
+        <v>1335.41</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4038.3</v>
+        <v>4004.1</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28260.91</v>
+        <v>28021.55</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>997.46</v>
+        <v>989.01</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1243.65</v>
+        <v>1233.12</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7368.68</v>
+        <v>7306.28</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4266.94</v>
+        <v>4230.81</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>811.39</v>
+        <v>804.52</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1015.29</v>
+        <v>1006.69</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4654.58</v>
+        <v>4615.16</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>943.66</v>
+        <v>935.67</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2219.15</v>
+        <v>2200.36</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1243.21</v>
+        <v>1232.68</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2884.81</v>
+        <v>2860.37</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8963.450000000001</v>
+        <v>8887.540000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>975.39</v>
+        <v>967.13</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1070.81</v>
+        <v>1061.74</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1021.52</v>
+        <v>1016.28</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>749.08</v>
+        <v>745.23</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>14027.41</v>
+        <v>13955.34</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2408.2</v>
+        <v>2395.83</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2838.1</v>
+        <v>2823.52</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1951.7</v>
+        <v>1941.67</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1301.37</v>
+        <v>1294.68</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1074.31</v>
+        <v>1068.79</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2220.27</v>
+        <v>2208.86</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1609.62</v>
+        <v>1601.35</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1718.43</v>
+        <v>1709.6</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1490.92</v>
+        <v>1483.26</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3033.37</v>
+        <v>3017.78</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5098.56</v>
+        <v>5072.36</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3311.2</v>
+        <v>3294.19</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1481.15</v>
+        <v>1473.54</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1449.95</v>
+        <v>1442.5</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3094.98</v>
+        <v>3079.08</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2336.04</v>
+        <v>2324.04</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3160.12</v>
+        <v>3143.88</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1456.02</v>
+        <v>1448.54</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2126.96</v>
+        <v>2116.03</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>947.91</v>
+        <v>943.04</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5646.86</v>
+        <v>5617.84</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1220.91</v>
+        <v>1214.63</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>765.9299999999999</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1338.46</v>
+        <v>1331.58</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5320.17</v>
+        <v>5292.83</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1822.46</v>
+        <v>1813.09</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7431.03</v>
+        <v>7392.85</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>772.02</v>
+        <v>764.3200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>766.13</v>
+        <v>758.49</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4746.72</v>
+        <v>4699.35</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1155.98</v>
+        <v>1144.45</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7834.16</v>
+        <v>7755.97</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3030.08</v>
+        <v>2999.84</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3479.56</v>
+        <v>3444.84</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3425.83</v>
+        <v>3391.64</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2073.04</v>
+        <v>2052.35</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2025.89</v>
+        <v>2005.68</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4846.95</v>
+        <v>4798.58</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1603.23</v>
+        <v>1587.23</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1123.31</v>
+        <v>1112.1</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2520.67</v>
+        <v>2495.51</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>972.29</v>
+        <v>962.59</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2046.88</v>
+        <v>2026.45</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1207.17</v>
+        <v>1195.13</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>861.1</v>
+        <v>852.51</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2003.89</v>
+        <v>1983.89</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1765.05</v>
+        <v>1747.43</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5327.8</v>
+        <v>5274.63</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>22020.85</v>
+        <v>21801.07</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2520.04</v>
+        <v>2494.89</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4170.16</v>
+        <v>4128.54</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1129.72</v>
+        <v>1118.45</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2482.26</v>
+        <v>2456.26</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1512.91</v>
+        <v>1497.06</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1699.22</v>
+        <v>1681.43</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>747.85</v>
+        <v>740.01</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1033.31</v>
+        <v>1022.49</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>793.83</v>
+        <v>785.51</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>832.22</v>
+        <v>823.51</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1219.89</v>
+        <v>1207.12</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2838.1</v>
+        <v>2808.38</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>782.03</v>
+        <v>773.84</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1664.16</v>
+        <v>1646.74</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3028.27</v>
+        <v>2996.55</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4895.71</v>
+        <v>4844.44</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>860.74</v>
+        <v>851.73</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>784.91</v>
+        <v>776.6900000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8711.469999999999</v>
+        <v>8620.24</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>19220.02</v>
+        <v>19018.74</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>9681.15</v>
+        <v>9579.76</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>14064.69</v>
+        <v>13917.4</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>790.33</v>
+        <v>782.0599999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2451.48</v>
+        <v>2425.81</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>744.6900000000001</v>
+        <v>736.89</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>11967.15</v>
+        <v>11841.83</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2812.22</v>
+        <v>2782.77</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1233.63</v>
+        <v>1220.71</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>24285.76</v>
+        <v>24031.43</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1431.01</v>
+        <v>1416.02</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1230</v>
+        <v>1217.12</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1120.1</v>
+        <v>1108.37</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3908.81</v>
+        <v>3867.88</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>7432.46</v>
+        <v>7391.84</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2900.04</v>
+        <v>2884.19</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1796.77</v>
+        <v>1786.95</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2456.67</v>
+        <v>2443.24</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1718.58</v>
+        <v>1709.18</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2441.81</v>
+        <v>2428.47</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>817.26</v>
+        <v>812.79</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2433.71</v>
+        <v>2420.41</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>10751.62</v>
+        <v>10692.85</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>17892.41</v>
+        <v>17794.62</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5447.28</v>
+        <v>5417.51</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>5340.33</v>
+        <v>5311.14</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4249.01</v>
+        <v>4225.79</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4638.18</v>
+        <v>4612.82</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3130.61</v>
+        <v>3113.5</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>978.8200000000001</v>
+        <v>973.47</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1322.27</v>
+        <v>1315.04</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6812.75</v>
+        <v>6775.52</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1925.19</v>
+        <v>1914.67</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>8350.17</v>
+        <v>8304.530000000001</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5400.02</v>
+        <v>5370.5</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>10547.35</v>
+        <v>10489.7</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1762.71</v>
+        <v>1753.08</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1067.91</v>
+        <v>1056.01</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5186.25</v>
+        <v>5128.46</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>891.34</v>
+        <v>881.41</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1713.44</v>
+        <v>1694.35</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>747.91</v>
+        <v>739.58</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1872.13</v>
+        <v>1851.28</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>910.21</v>
+        <v>900.0700000000001</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1030.29</v>
+        <v>1018.81</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2937.34</v>
+        <v>2904.61</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>755.0599999999999</v>
+        <v>746.65</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>18837.53</v>
+        <v>18627.65</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>748.77</v>
+        <v>740.4299999999999</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1862.39</v>
+        <v>1841.64</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5746.2</v>
+        <v>5682.18</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1056.48</v>
+        <v>1044.71</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1714.89</v>
+        <v>1695.79</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3276.86</v>
+        <v>3240.35</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2574.68</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1053.74</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>7042.54</v>
+        <v>6964.07</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>783.16</v>
+        <v>774.4400000000001</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>8182.62</v>
+        <v>8091.46</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>821.63</v>
+        <v>812.48</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1196.91</v>
+        <v>1183.57</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>807.83</v>
+        <v>798.83</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>872.4400000000001</v>
+        <v>862.72</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>870.05</v>
+        <v>860.36</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1094.49</v>
+        <v>1088.5</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>21009.1</v>
+        <v>20894.04</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>776.9299999999999</v>
+        <v>772.67</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1786.21</v>
+        <v>1776.43</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1407.95</v>
+        <v>1400.24</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2117.52</v>
+        <v>2105.93</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1096.31</v>
+        <v>1090.3</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1152.74</v>
+        <v>1146.43</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1185.42</v>
+        <v>1178.93</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10686.4</v>
+        <v>10627.87</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5182.5</v>
+        <v>5154.12</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3527.97</v>
+        <v>3508.65</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2142.25</v>
+        <v>2130.52</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2349.91</v>
+        <v>2337.04</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>10686.4</v>
+        <v>10627.87</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1361.82</v>
+        <v>1354.36</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2274.63</v>
+        <v>2262.17</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1242.65</v>
+        <v>1235.85</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1693.5</v>
+        <v>1684.23</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>12274.39</v>
+        <v>12207.17</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1741.42</v>
+        <v>1731.88</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>910.59</v>
+        <v>905.61</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2771.33</v>
+        <v>2756.16</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1246.09</v>
+        <v>1239.26</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1691.47</v>
+        <v>1682.2</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3347.85</v>
+        <v>3329.52</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2154.39</v>
+        <v>2142.59</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>745.55</v>
+        <v>741.46</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>744.88</v>
+        <v>740.8</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>36841.24</v>
+        <v>36639.48</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6167.94</v>
+        <v>6134.16</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4416.89</v>
+        <v>4392.7</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>8088.51</v>
+        <v>8044.22</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1409.56</v>
+        <v>1407.77</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>801.53</v>
+        <v>800.51</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1699.4</v>
+        <v>1697.23</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>748.11</v>
+        <v>747.16</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>851.0700000000001</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2151.91</v>
+        <v>2149.17</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3099.96</v>
+        <v>3096.01</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2186.82</v>
+        <v>2184.04</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2018.06</v>
+        <v>2015.49</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>747.6799999999999</v>
+        <v>746.73</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2061.11</v>
+        <v>2058.48</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>746.79</v>
+        <v>745.84</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>765.74</v>
+        <v>764.76</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1122.34</v>
+        <v>1120.92</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>745.84</v>
+        <v>744.89</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>3020.36</v>
+        <v>3016.51</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1616.99</v>
+        <v>1614.93</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>896.63</v>
+        <v>895.49</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1676.14</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>980.96</v>
+        <v>979.71</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>843.1900000000001</v>
+        <v>842.12</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4022.7</v>
+        <v>4017.58</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2513.1</v>
+        <v>2509.9</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1517.65</v>
+        <v>1515.71</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1296.45</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>937.4299999999999</v>
+        <v>936.23</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2555.45</v>
+        <v>2552.2</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3343.33</v>
+        <v>3339.08</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>6541.64</v>
+        <v>6533.31</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>5439.14</v>
+        <v>5432.22</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1866.97</v>
+        <v>1864.59</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1963.12</v>
+        <v>1960.62</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2014.5</v>
+        <v>2011.93</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>53777.47</v>
+        <v>53709.02</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1450.43</v>
+        <v>1448.59</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>759</v>
+        <v>758.03</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1239.86</v>
+        <v>1238.28</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1120.44</v>
+        <v>1119.01</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>746.38</v>
+        <v>745.4299999999999</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>927.84</v>
+        <v>926.66</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3273.23</v>
+        <v>3269.06</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>866.59</v>
+        <v>869.6799999999999</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>861.6799999999999</v>
+        <v>864.75</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>965.78</v>
+        <v>969.23</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1469.58</v>
+        <v>1474.82</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2136.56</v>
+        <v>2144.19</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2019.67</v>
+        <v>2026.88</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>4017.09</v>
+        <v>4031.43</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>4781.63</v>
+        <v>4798.7</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>7443.59</v>
+        <v>7470.16</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1190.72</v>
+        <v>1194.96</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2064.81</v>
+        <v>2072.18</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1471.21</v>
+        <v>1476.46</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>826.08</v>
+        <v>829.03</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3420.72</v>
+        <v>3432.93</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1005.15</v>
+        <v>1008.74</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>5012.91</v>
+        <v>5030.8</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>3621.39</v>
+        <v>3634.31</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2049.51</v>
+        <v>2056.82</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>29727.27</v>
+        <v>29833.36</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2726.06</v>
+        <v>2735.79</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1663.64</v>
+        <v>1669.57</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>772.66</v>
+        <v>775.42</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1395.83</v>
+        <v>1400.81</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>11929.23</v>
+        <v>11971.81</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1102.61</v>
+        <v>1106.55</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1133.15</v>
+        <v>1145.48</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1095.89</v>
+        <v>1107.8</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1392.24</v>
+        <v>1407.38</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1085.68</v>
+        <v>1097.49</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>923.99</v>
+        <v>934.04</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2338.8</v>
+        <v>2364.24</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2106.07</v>
+        <v>2128.97</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>850.61</v>
+        <v>859.87</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>6530.09</v>
+        <v>6601.11</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1082.07</v>
+        <v>1093.84</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1334.54</v>
+        <v>1349.06</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1096.21</v>
+        <v>1108.13</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2136.62</v>
+        <v>2159.86</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>747.8099999999999</v>
+        <v>755.95</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>749.71</v>
+        <v>757.87</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2027.08</v>
+        <v>2049.12</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>5234.64</v>
+        <v>5291.57</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1432.71</v>
+        <v>1448.3</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2127.69</v>
+        <v>2150.83</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>993.77</v>
+        <v>1004.58</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>860.92</v>
+        <v>870.28</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>7243.53</v>
+        <v>7322.32</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2982.7</v>
+        <v>3015.14</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>767.4</v>
+        <v>775.74</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>3560.95</v>
+        <v>3599.68</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1390.31</v>
+        <v>1405.43</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>6141.32</v>
+        <v>6208.12</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1160.92</v>
+        <v>1173.55</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1665.32</v>
+        <v>1683.43</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1265.17</v>
+        <v>1278.93</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2092.58</v>
+        <v>2115.34</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2986.08</v>
+        <v>3018.55</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1536.94</v>
+        <v>1553.66</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>4706.98</v>
+        <v>4758.17</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>5709.75</v>
+        <v>5771.85</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>791.97</v>
+        <v>800.58</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>745.78</v>
+        <v>748.24</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>5343.6</v>
+        <v>5361.18</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3623.9</v>
+        <v>3635.82</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2370.28</v>
+        <v>2378.07</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2323.41</v>
+        <v>2331.05</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>3229.73</v>
+        <v>3240.35</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2552.45</v>
+        <v>2560.85</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>21801.53</v>
+        <v>21873.24</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>743.3200000000001</v>
+        <v>745.76</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>998.8099999999999</v>
+        <v>1002.1</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>743.23</v>
+        <v>745.6799999999999</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1454.34</v>
+        <v>1459.13</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>744.15</v>
+        <v>746.6</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2137.4</v>
+        <v>2144.43</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>825.45</v>
+        <v>828.16</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>4171.03</v>
+        <v>4184.75</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>6752</v>
+        <v>6774.21</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2344.52</v>
+        <v>2352.24</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>757.3099999999999</v>
+        <v>759.8</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3714.45</v>
+        <v>3726.66</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1701.15</v>
+        <v>1706.75</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1223.59</v>
+        <v>1227.62</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>12824.93</v>
+        <v>12867.12</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3309.86</v>
+        <v>3366.99</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1278.14</v>
+        <v>1300.2</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>942.35</v>
+        <v>958.62</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>921.72</v>
+        <v>937.63</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>3529.39</v>
+        <v>3590.31</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3196.68</v>
+        <v>3251.86</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>956.01</v>
+        <v>972.51</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4215.95</v>
+        <v>4288.72</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>13933.34</v>
+        <v>14173.85</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>6447.43</v>
+        <v>6558.72</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>3578.78</v>
+        <v>3640.56</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>841.2</v>
+        <v>855.72</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1200.43</v>
+        <v>1221.15</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2917.26</v>
+        <v>2967.62</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>68697.42</v>
+        <v>69883.25</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2389.62</v>
+        <v>2430.87</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2141.68</v>
+        <v>2178.64</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1882.36</v>
+        <v>1914.85</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>855.21</v>
+        <v>869.97</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>4527.12</v>
+        <v>4605.27</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>4746.28</v>
+        <v>4828.21</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>12144.51</v>
+        <v>12354.15</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1319.97</v>
+        <v>1342.75</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>911.76</v>
+        <v>927.49</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>900.76</v>
+        <v>916.3099999999999</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1477.77</v>
+        <v>1503.28</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>14340.78</v>
+        <v>14588.32</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1340.52</v>
+        <v>1363.66</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1916.89</v>
+        <v>1949.98</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>3319.28</v>
+        <v>3376.58</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1075.77</v>
+        <v>1094.34</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>2404.41</v>
+        <v>2445.91</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>984.4299999999999</v>
+        <v>1001.42</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3058.79</v>
+        <v>3111.59</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>799.5700000000001</v>
+        <v>813.37</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1068.01</v>
+        <v>1086.45</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>2671.78</v>
+        <v>2717.9</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>14741.31</v>
+        <v>14995.77</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>7168.26</v>
+        <v>7292</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3059.9</v>
+        <v>3081.1</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>6247.97</v>
+        <v>6291.25</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2186.91</v>
+        <v>2202.06</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>758.3</v>
+        <v>763.55</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2581</v>
+        <v>2598.88</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1167.11</v>
+        <v>1175.2</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>888.49</v>
+        <v>894.64</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>809.77</v>
+        <v>815.38</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>763.54</v>
+        <v>768.83</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1723.51</v>
+        <v>1735.45</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2171.57</v>
+        <v>2186.61</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>5986.26</v>
+        <v>6027.73</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1068.62</v>
+        <v>1076.02</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1026.64</v>
+        <v>1033.76</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1382.34</v>
+        <v>1391.92</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>745.29</v>
+        <v>750.45</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2868.37</v>
+        <v>2888.24</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2625.78</v>
+        <v>2643.97</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>8227.690000000001</v>
+        <v>8284.690000000001</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1593.92</v>
+        <v>1604.96</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1545.69</v>
+        <v>1552.89</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1123.43</v>
+        <v>1128.66</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>2212.82</v>
+        <v>2223.12</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1798.74</v>
+        <v>1807.12</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>7505.15</v>
+        <v>7540.1</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1635.33</v>
+        <v>1642.95</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>2149.94</v>
+        <v>2159.95</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>7429.35</v>
+        <v>7463.95</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1977.25</v>
+        <v>1986.46</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>3379.88</v>
+        <v>3395.62</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>777.5700000000001</v>
+        <v>781.1900000000001</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1601.74</v>
+        <v>1609.2</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1104.57</v>
+        <v>1109.71</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2014.15</v>
+        <v>2023.53</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>5557.36</v>
+        <v>5583.24</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>977.15</v>
+        <v>981.7</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>2312.42</v>
+        <v>2323.19</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>829.45</v>
+        <v>833.3200000000001</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>1643.91</v>
+        <v>1651.56</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>889.27</v>
+        <v>893.41</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3059.9</v>
+        <v>3074.15</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1600.53</v>
+        <v>1607.99</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>7687</v>
+        <v>7722.8</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>767.85</v>
+        <v>771.42</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1412.36</v>
+        <v>1418.94</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2119.91</v>
+        <v>2135.2</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1035.89</v>
+        <v>1043.36</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>12992.49</v>
+        <v>13086.16</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>5788.43</v>
+        <v>5830.16</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1154.14</v>
+        <v>1162.46</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3816.29</v>
+        <v>3843.8</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>994.78</v>
+        <v>1001.95</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1676.23</v>
+        <v>1688.31</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1511.56</v>
+        <v>1522.46</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>3573.44</v>
+        <v>3599.21</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>4176.81</v>
+        <v>4206.93</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2385.97</v>
+        <v>2403.17</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1225.46</v>
+        <v>1234.29</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1023.04</v>
+        <v>1030.42</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2809.01</v>
+        <v>2829.26</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>5497.96</v>
+        <v>5537.6</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>9535.969999999999</v>
+        <v>9604.719999999999</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4269.97</v>
+        <v>4300.75</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>4133.2</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>6369.5</v>
+        <v>6415.42</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>3383.82</v>
+        <v>3408.22</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>4068.29</v>
+        <v>4097.62</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>11011.26</v>
+        <v>11090.65</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>915.86</v>
+        <v>922.46</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>785.03</v>
+        <v>790.6900000000001</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>2646.98</v>
+        <v>2666.06</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>2569.87</v>
+        <v>2588.4</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1015.55</v>
+        <v>1022.88</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1179.96</v>
+        <v>1188.46</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1663.65</v>
+        <v>1675.64</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2908.43</v>
+        <v>2929.4</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>960.47</v>
+        <v>967.39</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>934.5700000000001</v>
+        <v>941.3</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>1133.98</v>
+        <v>1142.16</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>776.7</v>
+        <v>782.3</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>854.87</v>
+        <v>861.03</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>3146.38</v>
+        <v>3169.06</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>5517.46</v>
+        <v>5557.24</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1129.88</v>
+        <v>1138.03</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>761.84</v>
+        <v>767.33</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>9567.969999999999</v>
+        <v>9636.950000000001</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>3796.77</v>
+        <v>3824.14</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>4226.34</v>
+        <v>4218.84</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>7548.51</v>
+        <v>7535.12</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>7222.85</v>
+        <v>7210.04</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>1228.44</v>
+        <v>1226.26</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1399.59</v>
+        <v>1397.11</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>5990.86</v>
+        <v>5980.23</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>763.17</v>
+        <v>761.8200000000001</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>1848.78</v>
+        <v>1845.51</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>2272.07</v>
+        <v>2268.04</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1341.73</v>
+        <v>1339.35</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2269.74</v>
+        <v>2265.72</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>1892.7</v>
+        <v>1889.34</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>2421.51</v>
+        <v>2417.22</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>3517.01</v>
+        <v>3510.77</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1234.58</v>
+        <v>1232.39</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>2134.04</v>
+        <v>2130.25</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>7486.83</v>
+        <v>7473.55</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>1039.89</v>
+        <v>1038.05</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>4340.55</v>
+        <v>4332.85</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1477.22</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>1255.14</v>
+        <v>1252.92</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3751.79</v>
+        <v>3745.13</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>745.62</v>
+        <v>744.3</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>3630.67</v>
+        <v>3624.23</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>851.77</v>
+        <v>850.26</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>23262.95</v>
+        <v>23221.69</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1340.2</v>
+        <v>1337.82</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>775.47</v>
+        <v>774.09</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>7134.86</v>
+        <v>7122.2</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>920.51</v>
+        <v>918.88</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1972.53</v>
+        <v>1969.03</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>747.42</v>
+        <v>744.34</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1449.09</v>
+        <v>1443.12</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1000.08</v>
+        <v>995.96</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1184.99</v>
+        <v>1180.11</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>789.39</v>
+        <v>786.14</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>6818.91</v>
+        <v>6790.8</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1441.27</v>
+        <v>1435.33</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2583.49</v>
+        <v>2572.84</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>796.85</v>
+        <v>793.5599999999999</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>3078.01</v>
+        <v>3065.32</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>1977.23</v>
+        <v>1969.08</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>1103.85</v>
+        <v>1099.3</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>1808.23</v>
+        <v>1800.78</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>966.09</v>
+        <v>962.11</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>866.59</v>
+        <v>863.02</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>3887.83</v>
+        <v>3871.8</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2081.45</v>
+        <v>2072.87</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>11367.29</v>
+        <v>11320.44</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>752.02</v>
+        <v>748.92</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>14909</v>
+        <v>14847.55</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>2332.7</v>
+        <v>2323.08</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>2039.68</v>
+        <v>2031.27</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>840.0599999999999</v>
+        <v>836.6</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1165.59</v>
+        <v>1160.78</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>16679.41</v>
+        <v>16610.66</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>7478.06</v>
+        <v>7447.24</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>2751.62</v>
+        <v>2740.28</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>3606.32</v>
+        <v>3591.46</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>744.17</v>
+        <v>741.1</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>951.72</v>
+        <v>947.8</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>1448.32</v>
+        <v>1442.35</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>759.39</v>
+        <v>756.26</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1958.45</v>
+        <v>1950.38</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1673.6</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>3001.72</v>
+        <v>2997.06</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2909</v>
+        <v>2904.49</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>999.09</v>
+        <v>997.54</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>36705.21</v>
+        <v>36648.32</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>5157.2</v>
+        <v>5149.21</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>3533.38</v>
+        <v>3527.91</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>3057.02</v>
+        <v>3052.28</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>4283.27</v>
+        <v>4276.64</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>941.7</v>
+        <v>940.24</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>1840.26</v>
+        <v>1837.41</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>2820.6</v>
+        <v>2816.23</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>19113.73</v>
+        <v>19084.11</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2249.06</v>
+        <v>2245.58</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>960.55</v>
+        <v>959.0599999999999</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>17871.67</v>
+        <v>17843.97</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1945.03</v>
+        <v>1942.01</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>744.09</v>
+        <v>742.9400000000001</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>3219.06</v>
+        <v>3214.07</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>767.42</v>
+        <v>766.23</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2592.14</v>
+        <v>2588.12</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1621.77</v>
+        <v>1619.26</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2698.21</v>
+        <v>2694.02</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>8861.120000000001</v>
+        <v>8847.379999999999</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1072.25</v>
+        <v>1070.59</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>20528.03</v>
+        <v>20496.22</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>751.49</v>
+        <v>750.3200000000001</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>12276.73</v>
+        <v>12257.7</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1216.33</v>
+        <v>1214.44</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>759.33</v>
+        <v>758.15</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1769.23</v>
+        <v>1766.49</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1725.8</v>
+        <v>1723.13</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2707.59</v>
+        <v>2703.39</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>1328.21</v>
+        <v>1335.07</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>1452.1</v>
+        <v>1459.6</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>908.55</v>
+        <v>913.24</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>1491.3</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>1333.08</v>
+        <v>1339.96</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>4693.12</v>
+        <v>4717.35</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2272.7</v>
+        <v>2284.44</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1134.85</v>
+        <v>1140.71</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1737.03</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>834.03</v>
+        <v>838.34</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>1153.45</v>
+        <v>1159.41</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>787.49</v>
+        <v>791.55</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>1646.95</v>
+        <v>1655.46</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>4689.16</v>
+        <v>4713.38</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>1440.67</v>
+        <v>1448.11</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>4961.01</v>
+        <v>4986.64</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1602.61</v>
+        <v>1610.89</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>2994.98</v>
+        <v>3010.45</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>18688.09</v>
+        <v>18784.6</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>5255.4</v>
+        <v>5282.54</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>2042.48</v>
+        <v>2053.02</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>834.26</v>
+        <v>838.5700000000001</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>756.96</v>
+        <v>760.87</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>4010.17</v>
+        <v>4030.88</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1066.63</v>
+        <v>1072.14</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>7824.21</v>
+        <v>7864.62</v>
       </c>
     </row>
     <row r="567">
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>2473.61</v>
+        <v>2486.38</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>1506.29</v>
+        <v>1514.07</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>3653.72</v>
+        <v>3672.59</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>3812.95</v>
+        <v>3839.86</v>
       </c>
     </row>
     <row r="571">
@@ -35278,7 +35278,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>1291.36</v>
+        <v>1300.48</v>
       </c>
     </row>
     <row r="572">
@@ -35339,7 +35339,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>3151.47</v>
+        <v>3173.71</v>
       </c>
     </row>
     <row r="573">
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1554.88</v>
+        <v>1565.85</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>1767.92</v>
+        <v>1780.4</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>3707.61</v>
+        <v>3733.77</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>2896.6</v>
+        <v>2917.05</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>4756.85</v>
+        <v>4790.42</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>8172.75</v>
+        <v>8230.43</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>3860.4</v>
+        <v>3887.64</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2776.63</v>
+        <v>2796.23</v>
       </c>
     </row>
     <row r="581">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>4277.92</v>
+        <v>4308.11</v>
       </c>
     </row>
     <row r="582">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>3014.85</v>
+        <v>3036.12</v>
       </c>
     </row>
     <row r="583">
@@ -36010,7 +36010,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>4347.65</v>
+        <v>4378.34</v>
       </c>
     </row>
     <row r="584">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2454.02</v>
+        <v>2471.34</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2305.46</v>
+        <v>2321.74</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>5064.91</v>
+        <v>5100.65</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>3937.04</v>
+        <v>3964.83</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1555.79</v>
+        <v>1566.77</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2546.76</v>
+        <v>2564.74</v>
       </c>
     </row>
     <row r="590">
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1862.86</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="591">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>1266.67</v>
+        <v>1275.61</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>2064.35</v>
+        <v>2078.92</v>
       </c>
     </row>
     <row r="593">
@@ -36620,7 +36620,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2484</v>
+        <v>2501.53</v>
       </c>
     </row>
     <row r="594">
@@ -36681,7 +36681,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>6072.43</v>
+        <v>6115.29</v>
       </c>
     </row>
     <row r="595">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2480.53</v>
+        <v>2498.04</v>
       </c>
     </row>
     <row r="596">
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>2556.77</v>
+        <v>2574.82</v>
       </c>
     </row>
     <row r="597">
@@ -36864,7 +36864,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>753.5700000000001</v>
+        <v>758.89</v>
       </c>
     </row>
     <row r="598">
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>741.11</v>
+        <v>746.34</v>
       </c>
     </row>
     <row r="599">
@@ -36986,7 +36986,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>837.08</v>
+        <v>842.99</v>
       </c>
     </row>
     <row r="600">
@@ -37047,7 +37047,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1729.3</v>
+        <v>1741.51</v>
       </c>
     </row>
     <row r="601">
@@ -37108,7 +37108,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>6367.76</v>
+        <v>6412.7</v>
       </c>
     </row>
     <row r="602">
@@ -37169,7 +37169,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>757.87</v>
+        <v>763.21</v>
       </c>
     </row>
     <row r="603">
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1072.87</v>
+        <v>1080.44</v>
       </c>
     </row>
     <row r="604">
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>2559.3</v>
+        <v>2577.36</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2030.5</v>
+        <v>2044.83</v>
       </c>
     </row>
     <row r="606">
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>12957.37</v>
+        <v>13048.82</v>
       </c>
     </row>
     <row r="607">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1108.83</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>1072.11</v>
+        <v>1079.68</v>
       </c>
     </row>
     <row r="609">
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>3877.65</v>
+        <v>3905.02</v>
       </c>
     </row>
     <row r="610">
@@ -37657,7 +37657,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>756.8</v>
+        <v>762.14</v>
       </c>
     </row>
     <row r="611">
@@ -37718,7 +37718,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>1491.03</v>
+        <v>1501.55</v>
       </c>
     </row>
     <row r="612">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>2326.22</v>
+        <v>2342.64</v>
       </c>
     </row>
     <row r="613">
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>23905.44</v>
+        <v>24074.15</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>3379.12</v>
+        <v>3402.96</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificacion</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL PERSONAL DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Municipalidad de Pemuco - Salud</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Departamento De Educacion Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>ASOCIACION CHILENA DE MUNICIPALIDADES</t>
+          <t>Asociación Chilena de Municipalidades</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL POZO AL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Sandra Gioconda Tello López</t>
+          <t>SANDRA GIOCONDA TELLO LÓPEZ</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Departamento De Educacion Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SEREMI IX</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL  E INMOB MAS COMERCIO LTDA.</t>
+          <t>Sociedad Comercial  e Inmob Mas Comercio Ltda.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Clínica Reproducción Humana UV</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Clínica Reproducción Humana UV</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18285,7 +18285,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Mineduc Administración X Región</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20674,12 +20674,12 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20735,12 +20735,12 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Adulto Mayor</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23663,7 +23663,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Economato Centro Detención Preventiva Puente Alto</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -25071,12 +25071,12 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27811,7 +27811,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -28360,7 +28360,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -29153,7 +29153,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -29275,7 +29275,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29519,7 +29519,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29763,7 +29763,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -31227,7 +31227,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32386,7 +32386,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -33667,7 +33667,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -34399,7 +34399,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -34887,7 +34887,7 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -35131,7 +35131,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35375,7 +35375,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35497,7 +35497,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36168,7 +36168,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -36595,7 +36595,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -37022,7 +37022,7 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -37144,7 +37144,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -37327,7 +37327,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIO</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -37388,7 +37388,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -37439,7 +37439,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
@@ -37449,7 +37449,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -37571,7 +37571,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -37703,7 +37703,7 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
@@ -37876,7 +37876,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/nov-2025.xlsx
@@ -562,7 +562,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>77.399.254-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2094,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2411,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2541,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2797,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2927,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3057,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3122,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3248,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3435,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3561,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3626,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3752,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3817,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4012,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4077,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4268,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4333,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4398,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4463,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4528,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4654,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4841,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4906,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5093,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5158,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5284,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5349,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5414,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5540,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5605,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5796,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5861,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5926,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6052,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6117,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6182,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6312,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6442,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6507,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6572,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6637,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6702,11 @@
           <t>77.911.731-6</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6767,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6832,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6958,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7023,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7088,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7153,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7218,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7344,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7409,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7474,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7539,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7604,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7734,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7799,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7925,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8051,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8177,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8242,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8307,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8372,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8437,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8502,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8628,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8693,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8819,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8884,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9071,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9136,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9201,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9331,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9396,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9583,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9648,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9713,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9778,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9843,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9908,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10103,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10168,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10481,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10546,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10611,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10676,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10741,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10806,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10871,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10936,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11066,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11131,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11196,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11261,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11326,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11391,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11521,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11586,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11956,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12143,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12330,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12521,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12586,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12651,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12716,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12968,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13033,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13163,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13228,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13293,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13358,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13671,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14301,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14549,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14675,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14740,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14805,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14870,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14935,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15000,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15126,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15191,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15256,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15443,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15508,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15634,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15886,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16012,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16142,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16455,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16585,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16711,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16776,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16906,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16971,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17036,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17101,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17166,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17353,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17418,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17544,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17609,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17674,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17739,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17804,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17991,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18056,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18121,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18247,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18438,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18564,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18629,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18755,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18820,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18885,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19011,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19141,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19206,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19336,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19401,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19653,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19779,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19844,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19909,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19974,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20039,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20104,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20169,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20234,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20299,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20364,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20494,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20559,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20624,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20689,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20754,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20819,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20884,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20949,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21014,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21079,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21144,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21270,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21335,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21461,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21774,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21839,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21904,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21969,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22034,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22099,11 @@
           <t>77.399.254-1</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22164,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22412,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22603,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22668,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22733,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22859,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22924,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22989,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23054,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23119,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23497,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23562,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23627,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23814,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23879,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24074,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24139,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24204,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24269,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24395,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24460,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24525,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24720,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24785,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +24850,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24915,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24980,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25106,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25171,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25236,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25362,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25427,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25492,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25557,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25622,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25687,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25878,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26126,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26191,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26317,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26382,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26447,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26512,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26642,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26902,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27028,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27154,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27284,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27349,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27414,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27601,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27796,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27861,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27926,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27991,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28117,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28182,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28308,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28434,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28499,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28564,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28629,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28694,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28759,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28824,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28889,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29015,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29080,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29145,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29210,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29275,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29340,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29405,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29531,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29596,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29722,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29848,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30222,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30348,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30413,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30478,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30543,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30608,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30673,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30738,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30864,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31051,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31116,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31242,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31307,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31372,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31498,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31563,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31628,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31754,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31819,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31884,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32079,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32144,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32209,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32339,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32404,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32530,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32786,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32851,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32916,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32981,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33046,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33111,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33237,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33302,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33432,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33558,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33623,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33688,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33814,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34139,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34204,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34269,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34334,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34399,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34525,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34716,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34781,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34846,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34911,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35037,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35163,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35350,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35598,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35663,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35728,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35793,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35858,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35923,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35988,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36053,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +36118,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36183,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36248,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36374,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36439,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36504,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36569,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +36634,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36764,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36890,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36955,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +37142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37398,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37463,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37772,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37959,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38024,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38211,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +38276,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38341,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38406,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38471,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +38536,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38601,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +38796,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38922,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +39048,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +39113,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +39178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39243,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39373,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39438,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39564,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39629,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39694,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
